--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487416_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487416_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.587</v>
+        <v>4.8614</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8707</v>
+        <v>7.8512</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2838</v>
+        <v>-2.9897</v>
       </c>
       <c r="G2" t="n">
         <v>3.5497</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4719</v>
+        <v>-0.1975</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0339</v>
+        <v>-0.0535</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.438</v>
+        <v>-0.1439</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0576</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7077</v>
+        <v>2.3843</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8573</v>
+        <v>2.2667</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1497</v>
+        <v>0.1176</v>
       </c>
       <c r="G3" t="n">
         <v>1.5953</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6711</v>
+        <v>0.0056</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7128</v>
+        <v>-0.3035</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0418</v>
+        <v>0.3091</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.68</v>
+        <v>1.9662</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7877</v>
+        <v>3.1541</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1077</v>
+        <v>-1.1879</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6761</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1899</v>
+        <v>0.0963</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2329</v>
+        <v>0.1335</v>
       </c>
       <c r="U4" t="n">
-        <v>0.043</v>
+        <v>-0.0372</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. IGOA ENDJILO</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2158</v>
+        <v>0.2054</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1949</v>
+        <v>-0.2196</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4107</v>
+        <v>0.425</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.852</v>
+        <v>0.8801</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.852</v>
+        <v>1.2743</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.3941</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5802</v>
+        <v>2.0259</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5802</v>
+        <v>2.0211</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2719</v>
+        <v>-1.1458</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2719</v>
+        <v>-0.7468</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2844</v>
+        <v>-0.2035</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3852</v>
+        <v>-0.287</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1008</v>
+        <v>0.0835</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>X. IGOA ENDJILO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3154</v>
+        <v>-0.1401</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5266</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2112</v>
+        <v>0.4642</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8801</v>
+        <v>-0.852</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2743</v>
+        <v>-0.852</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3941</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0259</v>
+        <v>-0.5802</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0211</v>
+        <v>-0.5802</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1458</v>
+        <v>-0.2719</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7468</v>
+        <v>-0.2719</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.399</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.594</v>
+        <v>-0.0241</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1303</v>
+        <v>-0.0473</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>M. IGLESIAS VALDERRAMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4684</v>
+        <v>-1.9327</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-1.771</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.381</v>
+        <v>-0.1617</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5276</v>
+        <v>-3.9318</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5836</v>
+        <v>-1.9867</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.944</v>
+        <v>-1.9451</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5712</v>
+        <v>-1.3788</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5204</v>
+        <v>-0.2212</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0508</v>
+        <v>-1.1576</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.0988</v>
+        <v>-2.553</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.104</v>
+        <v>-1.7655</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9948</v>
+        <v>-0.7875</v>
       </c>
       <c r="P7" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.9377</v>
+        <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7055</v>
+        <v>0.2745</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2584</v>
+        <v>0.3117</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4471</v>
+        <v>-0.0372</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3329</v>
+        <v>0.9412</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3329</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0076</v>
+        <v>-2.1044</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.211</v>
+        <v>-1.563</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7966</v>
+        <v>-0.5414</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.853</v>
+        <v>-2.5276</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2723</v>
+        <v>-1.5836</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4194</v>
+        <v>-0.944</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9042</v>
+        <v>1.5712</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4391</v>
+        <v>0.5204</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3433</v>
+        <v>1.0508</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7572</v>
+        <v>-4.0988</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8332</v>
+        <v>-2.104</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.924</v>
+        <v>-1.9948</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>2.546</v>
+        <v>2.9377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2371</v>
+        <v>1.0695</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3305</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0934</v>
+        <v>0.2867</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W8" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.492</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. IGLESIAS VALDERRAMA</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2189</v>
+        <v>-2.1307</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1374</v>
+        <v>-0.254</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0815</v>
+        <v>-1.8767</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9318</v>
+        <v>-1.853</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9867</v>
+        <v>-2.2723</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9451</v>
+        <v>0.4194</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3788</v>
+        <v>0.9042</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2212</v>
+        <v>-0.4391</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1576</v>
+        <v>1.3433</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.553</v>
+        <v>-2.7572</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7655</v>
+        <v>-1.8332</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7875</v>
+        <v>-0.924</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0117</v>
+        <v>0.114</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0547</v>
+        <v>0.2876</v>
       </c>
       <c r="U9" t="n">
-        <v>0.043</v>
+        <v>-0.1736</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>1.492</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6659</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7559</v>
+        <v>-3.3883</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3836</v>
+        <v>-4.5883</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6277</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0485</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9976</v>
+        <v>0.3652</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09</v>
+        <v>-0.2947</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0876</v>
+        <v>0.6599</v>
       </c>
       <c r="V10" t="n">
         <v>1.2742</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5756999999999999</v>
+        <v>-0.278900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.974799999999999</v>
+        <v>4.271800000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5507</v>
+        <v>-4.550599999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.8639</v>
+        <v>-7.863900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.837800000000001</v>
+        <v>-7.8378</v>
       </c>
       <c r="I11" t="n">
         <v>-0.02589999999999959</v>
@@ -1288,7 +1288,7 @@
         <v>13.9894</v>
       </c>
       <c r="K11" t="n">
-        <v>4.0414</v>
+        <v>4.041399999999999</v>
       </c>
       <c r="L11" t="n">
         <v>9.947999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>18.6054</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1557</v>
+        <v>1.4526</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2557999999999999</v>
+        <v>0.5528000000000002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="V11" t="n">
         <v>2.2153</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6307</v>
+        <v>4.9507</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8444</v>
+        <v>4.4585</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7863</v>
+        <v>0.4923</v>
       </c>
       <c r="G12" t="n">
         <v>3.3055</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2842</v>
+        <v>0.0357</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9745</v>
+        <v>-0.3605</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6903</v>
+        <v>0.3963</v>
       </c>
       <c r="V12" t="n">
         <v>0.8260999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1269</v>
+        <v>1.9056</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0885</v>
+        <v>0.7815</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0384</v>
+        <v>1.1242</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2591</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4275</v>
+        <v>0.2063</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3435</v>
+        <v>0.0365</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1698</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5105</v>
+        <v>1.8295</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8726</v>
+        <v>0.9749</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6379</v>
+        <v>0.8545</v>
       </c>
       <c r="G14" t="n">
         <v>1.0653</v>
@@ -1546,13 +1546,13 @@
         <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3382</v>
+        <v>-0.0193</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2194</v>
+        <v>-0.0028</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0932</v>
+        <v>1.7624</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9842</v>
+        <v>2.0865</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.891</v>
+        <v>-0.3241</v>
       </c>
       <c r="G15" t="n">
         <v>4.4667</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9438</v>
+        <v>-0.2745</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4529</v>
+        <v>-0.3505</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4909</v>
+        <v>0.076</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.129</v>
+        <v>0.107</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1307</v>
+        <v>-0.0284</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0017</v>
+        <v>0.1353</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0223</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6943</v>
+        <v>-0.4583</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4567</v>
+        <v>-0.323</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1364</v>
+        <v>-0.3263</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7168</v>
+        <v>2.3074</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8532</v>
+        <v>-2.6337</v>
       </c>
       <c r="G17" t="n">
         <v>0.6639</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3208</v>
+        <v>0.1309</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.1717</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2603</v>
+        <v>-0.0409</v>
       </c>
       <c r="V17" t="n">
         <v>-2.1003</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7638</v>
+        <v>-0.6341</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.995</v>
+        <v>-0.8508</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2311</v>
+        <v>0.2167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1394</v>
+        <v>0.8457</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3114</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.172</v>
+        <v>0.0508</v>
       </c>
       <c r="J18" t="n">
-        <v>1.405</v>
+        <v>2.2364</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1021</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3029</v>
+        <v>1.3789</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2656</v>
+        <v>-1.3906</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2094</v>
+        <v>-0.0625</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.475</v>
+        <v>-1.3281</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1543</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7004</v>
+        <v>-0.0501</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0129</v>
+        <v>-0.1494</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7134</v>
+        <v>0.0993</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5507</v>
+        <v>0.3329</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.284</v>
+        <v>-1.0533</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2601</v>
+        <v>-1.0973</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0239</v>
+        <v>0.044</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8457</v>
+        <v>0.1394</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.3114</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0508</v>
+        <v>-0.172</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2364</v>
+        <v>1.405</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.1021</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3789</v>
+        <v>1.3029</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3906</v>
+        <v>-1.2656</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0625</v>
+        <v>0.2094</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3281</v>
+        <v>-1.475</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7626</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7000999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5587</v>
+        <v>-0.1153</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1413</v>
+        <v>0.5262</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3329</v>
+        <v>0.5507</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0856</v>
+        <v>-2.9743</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5651</v>
+        <v>-2.4861</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5205</v>
+        <v>-0.4882</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8116</v>
@@ -2014,13 +2014,13 @@
         <v>2.546</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3711</v>
+        <v>0.4824</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0304</v>
+        <v>0.1094</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3407</v>
+        <v>0.373</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2742</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3866</v>
+        <v>-3.627</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0049</v>
+        <v>-1.5956</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3817</v>
+        <v>-2.0314</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5296</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0149</v>
+        <v>-0.2553</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4993</v>
+        <v>-0.09</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.1653</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5759000000000007</v>
+        <v>1.9402</v>
       </c>
       <c r="E22" t="n">
-        <v>4.550699999999999</v>
+        <v>4.5506</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9749</v>
+        <v>-2.6104</v>
       </c>
       <c r="G22" t="n">
         <v>7.863899999999999</v>
@@ -2170,13 +2170,13 @@
         <v>14.6885</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1557</v>
+        <v>0.2087999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8997000000000002</v>
+        <v>-0.8999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2557999999999999</v>
+        <v>1.1086</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2156</v>
